--- a/01.SOMD/01.metadata_structure/04_SOMD_selection_criteria.xlsx
+++ b/01.SOMD/01.metadata_structure/04_SOMD_selection_criteria.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Knolwedge_Hub/01.SOMD/01.metadata_structure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/01.SOMD/01.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="8_{3EECDAF2-0819-4BE9-B8AB-A24F34139E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797BFF37-218A-4637-B241-8F6B249E6A8D}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="8_{3EECDAF2-0819-4BE9-B8AB-A24F34139E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CE4F41-060A-4B6C-BFA5-0D48EB20BFE3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{CABD3BDC-3CCE-4943-9CF6-E440E1C2E72E}"/>
+    <workbookView minimized="1" xWindow="4110" yWindow="3870" windowWidth="21600" windowHeight="11175" xr2:uid="{CABD3BDC-3CCE-4943-9CF6-E440E1C2E72E}"/>
   </bookViews>
   <sheets>
     <sheet name="05_SOMD_selection_criteria" sheetId="1" r:id="rId1"/>
     <sheet name="05_SOMD_readme" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1293,8 +1293,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -1313,6 +1324,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1370,6 +1382,11 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1487,17 +1504,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1508,10 +1514,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02E85A0C-9939-4B2E-A0E9-B2795626D9D6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE21F537-F8C6-45BB-8614-D547AB26632C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1522,6 +1524,10 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE4DA0A0-DF34-48EE-A7DE-4E9965008367}"/>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31325C92-417A-44AE-8DF9-7F3FF1A39FE4}">
   <ds:schemaRefs>
